--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7560A295-0988-4AB2-8556-275F1A67C204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B36888EB386D070D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82C7A7A1-F65A-49D3-B87F-E3098A5B597C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 09-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 14-09-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B36888EB386D070D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82C7A7A1-F65A-49D3-B87F-E3098A5B597C}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B3678B63390C070D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF20BCA2-0E74-4E87-ABD4-1426AE747D0F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B3678B63390C070D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF20BCA2-0E74-4E87-ABD4-1426AE747D0F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31CD536-AFCD-4C8E-A7C0-3CCA03AAC768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31CD536-AFCD-4C8E-A7C0-3CCA03AAC768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201CC94D-51D0-4FD7-B57E-B474668D449E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 14-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 17-09-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201CC94D-51D0-4FD7-B57E-B474668D449E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35253B87-2E85-47E3-BE8C-0067D5C8B7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35253B87-2E85-47E3-BE8C-0067D5C8B7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B36A2F6B0BE4071D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C7561F1-9180-47D9-BF5E-E2F35E44A6A5}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 17-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 18-09-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B36A2F6B0BE4071D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C7561F1-9180-47D9-BF5E-E2F35E44A6A5}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B369996F4B1D671D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82256EDD-4EF5-426D-B8B0-6BD9344668BA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 18-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 21-09-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B369996F4B1D671D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82256EDD-4EF5-426D-B8B0-6BD9344668BA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5977E0-5EEE-4154-B88B-9A75A0BB7A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5977E0-5EEE-4154-B88B-9A75A0BB7A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77063911-0531-4F5E-A2A9-64A0997891F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 21-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 22-09-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77063911-0531-4F5E-A2A9-64A0997891F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8088FC5-4415-4A4C-BA4C-DE6FC11A19A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8088FC5-4415-4A4C-BA4C-DE6FC11A19A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D1465D-D10A-47C1-83B8-2F1F1138D668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 22-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 23-09-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D1465D-D10A-47C1-83B8-2F1F1138D668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B368AB6B481E071D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82BA8B39-F2CD-4862-946E-9599AF98E4F6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B368AB6B481E071D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82BA8B39-F2CD-4862-946E-9599AF98E4F6}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B364176F5B2EA70D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE57F4E4-999B-4B40-985C-10804CC25836}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 23-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 24-09-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B364176F5B2EA70D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE57F4E4-999B-4B40-985C-10804CC25836}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B362FEE30A69A71D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{117252CA-B722-4E6E-BE78-E4767BD51288}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B362FEE30A69A71D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{117252CA-B722-4E6E-BE78-E4767BD51288}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C7885E-316A-4F60-9EF2-73DE83363C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 24-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 28-09-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C7885E-316A-4F60-9EF2-73DE83363C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B36CA963681C070D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1CBE570-50E6-41CE-86CA-1462A1EE1029}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 28-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 02-10-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8088FC5-4415-4A4C-BA4C-DE6FC11A19A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A831472F-1073-4C60-A196-C4DB72064F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 22-09-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 07-10-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B36CA963681C070D869F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1CBE570-50E6-41CE-86CA-1462A1EE1029}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1B8A3D-071C-428A-B2F2-D278173D985F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 02-10-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 07-10-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -524,9 +524,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -622,7 +622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -654,7 +654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -793,7 +793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -822,7 +822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -851,7 +851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -880,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -941,7 +941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -964,7 +964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>51</v>
       </c>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1B8A3D-071C-428A-B2F2-D278173D985F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B368E2E70A0A071D869F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E060EC8-402F-4180-8837-BF7191DD049F}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 07-10-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 08-10-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B368E2E70A0A071D869F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E060EC8-402F-4180-8837-BF7191DD049F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EEC3FC-2B9E-45DF-947F-4429DB04FDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 08-10-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 09-10-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EEC3FC-2B9E-45DF-947F-4429DB04FDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80464FBB-D467-4849-AFE4-E296A17CC47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Kiropraktorsystemer_excel.XLSX
+++ b/html/Kiropraktorsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80464FBB-D467-4849-AFE4-E296A17CC47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94465F78CB58B362CAEB6BF0E70D869F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{881030CA-2C40-4FFF-A5F1-BBC642C417BA}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Kiropraktorsystemer">'Opdateret d. 09-10-2026'!$A$1:$J$32</definedName>
+    <definedName name="Kiropraktorsystemer">'Opdateret d. 23-10-2026'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
